--- a/human_resources_forms/027_diversity_equity_and_inclusion_dei_audit_checklist--human_resources_forms.xlsx
+++ b/human_resources_forms/027_diversity_equity_and_inclusion_dei_audit_checklist--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>leadership_accountability</t>
+          <t>leadership_accountability_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How does your organization hold leaders accountable for promoting diversity and inclusion?</t>
+          <t>Leadership Accountability 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>incident_reporting</t>
+          <t>incident_reporting_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>leadership_participation</t>
+          <t>leadership_participation_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is the level of leadership participation in DEI efforts?</t>
+          <t>Leadership Participation 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>communication_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How does the organization communicate about diversity and inclusion efforts?</t>
+          <t>Communication 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>diversity_outreach</t>
+          <t>diversity_outreach_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Are there programs to promote diversity outreach and engagement?</t>
+          <t>Diversity Outreach 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>leadership_accountability_choices</t>
+          <t>leadership_accountability_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>leadership_accountability_choices</t>
+          <t>leadership_accountability_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>leadership_accountability_choices</t>
+          <t>leadership_accountability_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>leadership_accountability_choices</t>
+          <t>leadership_accountability_2_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>leadership_accountability_choices</t>
+          <t>leadership_accountability_2_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>leadership_accountability_choices</t>
+          <t>leadership_accountability_2_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2384,7 +2384,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>leadership_accountability_choices</t>
+          <t>leadership_accountability_2_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>leadership_accountability_choices</t>
+          <t>leadership_accountability_2_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2996,7 +2996,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>incident_reporting_2_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>incident_reporting_2_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>incident_reporting_2_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>incident_reporting_2_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>incident_reporting_2_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>incident_reporting_2_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>incident_reporting_2_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>leadership_participation_choices</t>
+          <t>leadership_participation_2_choices</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>leadership_participation_choices</t>
+          <t>leadership_participation_2_choices</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>leadership_participation_choices</t>
+          <t>leadership_participation_2_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3404,7 +3404,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>leadership_participation_choices</t>
+          <t>leadership_participation_2_choices</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>leadership_participation_choices</t>
+          <t>leadership_participation_2_choices</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>leadership_participation_choices</t>
+          <t>leadership_participation_2_choices</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3489,7 +3489,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3540,7 +3540,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>diversity_outreach_choices</t>
+          <t>diversity_outreach_2_choices</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>diversity_outreach_choices</t>
+          <t>diversity_outreach_2_choices</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>diversity_outreach_choices</t>
+          <t>diversity_outreach_2_choices</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>diversity_outreach_choices</t>
+          <t>diversity_outreach_2_choices</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3642,7 +3642,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>diversity_outreach_choices</t>
+          <t>diversity_outreach_2_choices</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>diversity_outreach_choices</t>
+          <t>diversity_outreach_2_choices</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3676,7 +3676,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>diversity_outreach_choices</t>
+          <t>diversity_outreach_2_choices</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3693,7 +3693,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>diversity_outreach_choices</t>
+          <t>diversity_outreach_2_choices</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
